--- a/Experimentación de Algoritmos de Ordenamiento.xlsx
+++ b/Experimentación de Algoritmos de Ordenamiento.xlsx
@@ -91,52 +91,52 @@
     <t>STRING VARIABLE</t>
   </si>
   <si>
-    <t>605.9533 milisegundos</t>
-  </si>
-  <si>
-    <t>2862.3510 milisegundos</t>
-  </si>
-  <si>
-    <t>584.5389 milisegundos</t>
-  </si>
-  <si>
-    <t>2792.9500 milisegundos</t>
-  </si>
-  <si>
-    <t>688.8528 milisegundos</t>
-  </si>
-  <si>
-    <t>2706.6370 milisegundos</t>
-  </si>
-  <si>
-    <t>622.0120 milisegundos</t>
-  </si>
-  <si>
-    <t>2749.7070 milisegundos</t>
-  </si>
-  <si>
-    <t>636.2374 milisegundos</t>
-  </si>
-  <si>
-    <t>2735.3880 milisegundos</t>
-  </si>
-  <si>
-    <t>762.9270 milisegundos</t>
-  </si>
-  <si>
-    <t>3011.2780 milisegundos</t>
-  </si>
-  <si>
-    <t>1037.1311 milisegundos</t>
-  </si>
-  <si>
-    <t>3218.7200 milisegundos</t>
-  </si>
-  <si>
-    <t>1752.8210 milisegundos</t>
-  </si>
-  <si>
-    <t>3941.7510 milisegundos</t>
+    <t>593.6195 milisegundos</t>
+  </si>
+  <si>
+    <t>3022.3550 milisegundos</t>
+  </si>
+  <si>
+    <t>571.6696 milisegundos</t>
+  </si>
+  <si>
+    <t>2853.4030 milisegundos</t>
+  </si>
+  <si>
+    <t>572.4152 milisegundos</t>
+  </si>
+  <si>
+    <t>2706.8720 milisegundos</t>
+  </si>
+  <si>
+    <t>585.0886 milisegundos</t>
+  </si>
+  <si>
+    <t>2450.8140 milisegundos</t>
+  </si>
+  <si>
+    <t>646.4335 milisegundos</t>
+  </si>
+  <si>
+    <t>2612.9440 milisegundos</t>
+  </si>
+  <si>
+    <t>771.3135 milisegundos</t>
+  </si>
+  <si>
+    <t>2702.4320 milisegundos</t>
+  </si>
+  <si>
+    <t>1056.8280 milisegundos</t>
+  </si>
+  <si>
+    <t>3042.5890 milisegundos</t>
+  </si>
+  <si>
+    <t>1651.8810 milisegundos</t>
+  </si>
+  <si>
+    <t>3797.6190 milisegundos</t>
   </si>
   <si>
     <t>Valor del Umbral Tiempo QuickSort</t>
@@ -156,7 +156,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +168,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -212,7 +218,7 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -533,7 +539,7 @@
     <col min="5" max="5" style="7" width="21.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,7 +556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="3">
         <v>2</v>
       </c>
@@ -565,7 +571,7 @@
       </c>
       <c r="E2" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="3">
         <v>4</v>
       </c>
@@ -580,7 +586,7 @@
       </c>
       <c r="E3" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="3">
         <v>8</v>
       </c>
@@ -595,7 +601,7 @@
       </c>
       <c r="E4" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="3">
         <v>16</v>
       </c>
@@ -610,7 +616,7 @@
       </c>
       <c r="E5" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="3">
         <v>32</v>
       </c>
@@ -625,7 +631,7 @@
       </c>
       <c r="E6" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="3">
         <v>64</v>
       </c>
@@ -640,7 +646,7 @@
       </c>
       <c r="E7" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="3">
         <v>128</v>
       </c>
@@ -655,7 +661,7 @@
       </c>
       <c r="E8" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="3">
         <v>256</v>
       </c>
@@ -684,7 +690,7 @@
       <c r="D11" s="5"/>
       <c r="E11" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +707,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -716,7 +722,7 @@
       </c>
       <c r="E13" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="3">
         <v>4</v>
       </c>
@@ -731,7 +737,7 @@
       </c>
       <c r="E14" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="3">
         <v>8</v>
       </c>
@@ -746,7 +752,7 @@
       </c>
       <c r="E15" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="3">
         <v>16</v>
       </c>
@@ -761,7 +767,7 @@
       </c>
       <c r="E16" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="3">
         <v>32</v>
       </c>
@@ -776,7 +782,7 @@
       </c>
       <c r="E17" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="3">
         <v>64</v>
       </c>
@@ -791,7 +797,7 @@
       </c>
       <c r="E18" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="3">
         <v>128</v>
       </c>
@@ -806,7 +812,7 @@
       </c>
       <c r="E19" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="3">
         <v>256</v>
       </c>
@@ -849,7 +855,7 @@
       <c r="D24" s="5"/>
       <c r="E24" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
